--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40116,6 +40116,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1729" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="D1729" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="G1729" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40139,6 +40139,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1730">
+      <c r="A1730" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1730" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1730" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="D1730" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="F1730" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="G1730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40162,6 +40162,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1731">
+      <c r="A1731" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1731" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1731" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="D1731" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="F1731" t="n">
+        <v>0.165999993681908</v>
+      </c>
+      <c r="G1731" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1732" t="n">
+        <v>15600</v>
+      </c>
+      <c r="C1732" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="D1732" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="G1732" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40208,6 +40208,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1733">
+      <c r="A1733" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1733" t="n">
+        <v>21200</v>
+      </c>
+      <c r="C1733" t="n">
+        <v>0.160999998450279</v>
+      </c>
+      <c r="D1733" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>0.160999998450279</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="G1733" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40049,10 +40049,10 @@
     </row>
     <row r="1726">
       <c r="A1726" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1726" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="C1726" t="n">
         <v>0.165999993681908</v>
@@ -40072,10 +40072,10 @@
     </row>
     <row r="1727">
       <c r="A1727" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1727" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="C1727" t="n">
         <v>0.165999993681908</v>
@@ -40095,7 +40095,7 @@
     </row>
     <row r="1728">
       <c r="A1728" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1728" t="n">
         <v>0</v>
@@ -40118,7 +40118,7 @@
     </row>
     <row r="1729">
       <c r="A1729" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1729" t="n">
         <v>0</v>
@@ -40141,7 +40141,7 @@
     </row>
     <row r="1730">
       <c r="A1730" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1730" t="n">
         <v>0</v>
@@ -40164,7 +40164,7 @@
     </row>
     <row r="1731">
       <c r="A1731" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1731" t="n">
         <v>0</v>
@@ -40187,22 +40187,22 @@
     </row>
     <row r="1732">
       <c r="A1732" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1732" t="n">
-        <v>15600</v>
+        <v>0</v>
       </c>
       <c r="C1732" t="n">
-        <v>0.162000000476837</v>
+        <v>0.165999993681908</v>
       </c>
       <c r="D1732" t="n">
-        <v>0.162000000476837</v>
+        <v>0.165999993681908</v>
       </c>
       <c r="E1732" t="n">
-        <v>0.162000000476837</v>
+        <v>0.165999993681908</v>
       </c>
       <c r="F1732" t="n">
-        <v>0.162000000476837</v>
+        <v>0.165999993681908</v>
       </c>
       <c r="G1732" t="s">
         <v>7</v>
@@ -40210,24 +40210,47 @@
     </row>
     <row r="1733">
       <c r="A1733" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1733" t="n">
-        <v>21200</v>
+        <v>15600</v>
       </c>
       <c r="C1733" t="n">
-        <v>0.160999998450279</v>
+        <v>0.162000000476837</v>
       </c>
       <c r="D1733" t="n">
-        <v>0.159999996423721</v>
+        <v>0.162000000476837</v>
       </c>
       <c r="E1733" t="n">
-        <v>0.160999998450279</v>
+        <v>0.162000000476837</v>
       </c>
       <c r="F1733" t="n">
-        <v>0.159999996423721</v>
+        <v>0.162000000476837</v>
       </c>
       <c r="G1733" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1734" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1734" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="D1734" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="G1734" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -45511,6 +45511,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1737">
+      <c r="A1737" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1737" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C1737" t="n">
+        <v>0.155000001192093</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>0.155000001192093</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>0.155000001192093</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>0.155000001192093</v>
+      </c>
+      <c r="G1737" t="n">
+        <v>0.155000001192093</v>
+      </c>
+      <c r="H1737" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -45537,6 +45537,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1738">
+      <c r="A1738" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1738" t="n">
+        <v>166000</v>
+      </c>
+      <c r="C1738" t="n">
+        <v>0.185000002384186</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>0.180000007152557</v>
+      </c>
+      <c r="G1738" t="n">
+        <v>0.180000007152557</v>
+      </c>
+      <c r="H1738" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -45563,6 +45563,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1739">
+      <c r="A1739" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1739" t="n">
+        <v>224000</v>
+      </c>
+      <c r="C1739" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>0.166500002145767</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>0.181999996304512</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="G1739" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="H1739" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -45589,6 +45589,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1740">
+      <c r="A1740" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1740" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C1740" t="n">
+        <v>0.172000005841255</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>0.172000005841255</v>
+      </c>
+      <c r="G1740" t="n">
+        <v>0.172000005841255</v>
+      </c>
+      <c r="H1740" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -45667,6 +45667,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1743">
+      <c r="A1743" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1743" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C1743" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="D1743" t="n">
+        <v>0.16949999332428</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>0.16949999332428</v>
+      </c>
+      <c r="G1743" t="n">
+        <v>0.16949999332428</v>
+      </c>
+      <c r="H1743" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40507,6 +40507,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1746">
+      <c r="A1746" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B1746" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1746" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="D1746" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="G1746" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1747" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C1747" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="F1747"/>
+      <c r="G1747" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40546,8 +40546,31 @@
       <c r="E1747" t="n">
         <v>0.162000000476837</v>
       </c>
-      <c r="F1747"/>
+      <c r="F1747" t="n">
+        <v>0.170000001788139</v>
+      </c>
       <c r="G1747" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1748" t="n">
+        <v>54400</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>0.194999992847443</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>0.172999992966652</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>0.172999992966652</v>
+      </c>
+      <c r="F1748"/>
+      <c r="G1748" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40569,8 +40569,31 @@
       <c r="E1748" t="n">
         <v>0.172999992966652</v>
       </c>
-      <c r="F1748"/>
+      <c r="F1748" t="n">
+        <v>0.184000000357628</v>
+      </c>
       <c r="G1748" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1749" t="n">
+        <v>43200</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>0.195999994874001</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>0.19200000166893</v>
+      </c>
+      <c r="F1749"/>
+      <c r="G1749" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40592,7 +40592,9 @@
       <c r="E1749" t="n">
         <v>0.19200000166893</v>
       </c>
-      <c r="F1749"/>
+      <c r="F1749" t="n">
+        <v>0.17399999499321</v>
+      </c>
       <c r="G1749" t="s">
         <v>7</v>
       </c>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40622,6 +40622,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1751" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="G1751" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40645,6 +40645,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1752">
+      <c r="A1752" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1752" t="n">
+        <v>6800</v>
+      </c>
+      <c r="C1752" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="G1752" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -40668,6 +40668,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1753">
+      <c r="A1753" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B1753" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1753" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="D1753" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>0.17399999499321</v>
+      </c>
+      <c r="G1753" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -51273,6 +51273,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1756">
+      <c r="A1756" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1756" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1756" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="F1756" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="G1756" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="H1756" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1756" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1757" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1757" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="G1757" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="H1757" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1757" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -51331,6 +51331,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1758">
+      <c r="A1758" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1758" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1758" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="D1758" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="G1758" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="H1758" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1758" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -51360,6 +51360,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1759">
+      <c r="A1759" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1759" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1759" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="D1759" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="G1759" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="H1759" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1759" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -51389,6 +51389,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1760">
+      <c r="A1760" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1760" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1760" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="G1760" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="H1760" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1760" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -51418,6 +51418,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1761">
+      <c r="A1761" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1761" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1761" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="D1761" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="G1761" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="H1761" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1761" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -51447,6 +51447,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1762">
+      <c r="A1762" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1762" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1762" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="D1762" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="G1762" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="H1762" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1762" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -51476,6 +51476,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1763">
+      <c r="A1763" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1763" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1763" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="D1763" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F1763" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="G1763" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="H1763" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1763" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/U24.MI.xlsx
+++ b/data/U24.MI.xlsx
@@ -51505,6 +51505,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1764">
+      <c r="A1764" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1764" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1764" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="D1764" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="G1764" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="H1764" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1764" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
